--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¦ÃÂ¸ÃÂ¸ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¦ÃÂÃÂ¸ÃÂÃÂ¸ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¦ÃÂ¸ÃÂ¸ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¦ÃÂÃÂ¸ÃÂÃÂ¸ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -790,9 +790,6 @@
       <c r="G3" s="3" t="str">
         <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures supplémentaires","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Établir","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.historique","label":"Historique des voyages","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
       </c>
-      <c r="H3" s="3" t="str">
-        <v>{"matricule":"70000049","nom":"Pongo Pongo Charles","departement":"Lab","grade":"D2","jobTitle":"Quality Assurance Manager","localisation":""}</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¦ÃÂÃÂ¸ÃÂÃÂ¸ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¦ÃÂÃÂ¸ÃÂÃÂ¸ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -770,7 +770,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="str">
-        <v>berthe.lubenzo</v>
+        <v>berth.lubenzo</v>
       </c>
       <c r="B3" s="3" t="str">
         <v>Berthe Lubenzo</v>

--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -773,7 +773,7 @@
         <v>berth.lubenzo</v>
       </c>
       <c r="B3" s="3" t="str">
-        <v>Berthe Lubenzo</v>
+        <v>Berth Lubenzo</v>
       </c>
       <c r="C3" s="3" t="str">
         <v>BL</v>

--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -765,7 +765,7 @@
         <v>Actif</v>
       </c>
       <c r="G2" s="3" t="str">
-        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"project.projects","label":"Projects","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.historique","label":"Historique des voyages","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.etablir","label":"Établir","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.liste","label":"Factures fournisseur — Liste","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.factures","label":"Factures fournisseur — Factures","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.fournisseurs","label":"Factures fournisseur — Fournisseurs","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"sante","label":"Santé","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.club-house","label":"Club house","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.guest-house","label":"Guest house","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.departements","label":"Départements","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}}]</v>
+        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"project.projects","label":"Projects","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"sante","label":"Santé","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.departements","label":"Départements","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}}]</v>
       </c>
     </row>
     <row r="3">

--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -788,7 +788,7 @@
         <v>Actif</v>
       </c>
       <c r="G3" s="3" t="str">
-        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures supplémentaires","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Établir","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.historique","label":"Historique des voyages","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
+        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.54296875"/>
     <col min="2" max="2" customWidth="1" width="13.6328125"/>
@@ -791,10 +791,36 @@
         <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="str">
+        <v>Serge.Muakasa</v>
+      </c>
+      <c r="B4" s="3" t="str">
+        <v>Serge Muakasa</v>
+      </c>
+      <c r="C4" s="3" t="str">
+        <v>SM</v>
+      </c>
+      <c r="D4" s="3" t="str">
+        <v>Serge.Muakasa@ppcdrc.cd</v>
+      </c>
+      <c r="E4" s="3" t="str">
+        <v>123</v>
+      </c>
+      <c r="F4" s="3" t="str">
+        <v>Actif</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <v>{"matricule":"70000008","nom":"MUAKASA NSONI SERGE","departement":"Human Resources","grade":"C4","jobTitle":"Estate Officer","localisation":"Zamba"}</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.54296875"/>
     <col min="2" max="2" customWidth="1" width="13.6328125"/>
@@ -813,14 +813,40 @@
       <c r="G4" s="3" t="str">
         <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H4" s="3" t="str">
         <v>{"matricule":"70000008","nom":"MUAKASA NSONI SERGE","departement":"Human Resources","grade":"C4","jobTitle":"Estate Officer","localisation":"Zamba"}</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="str">
+        <v>Pelagie.Kinkinia</v>
+      </c>
+      <c r="B5" s="3" t="str">
+        <v>Pelagie Kinkinia</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <v>PK</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <v>Pelagie.Kinkinia@ppcdrc.cd</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <v>123</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <v>Actif</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <v>{"matricule":"70000295","nom":"KINKINIA DIAVEZUKA PELAGIE","departement":"Administration","grade":"D2","jobTitle":"Plant HR Manager","localisation":"Zamba"}</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.54296875"/>
     <col min="2" max="2" customWidth="1" width="13.6328125"/>
@@ -843,10 +843,36 @@
         <v>{"matricule":"70000295","nom":"KINKINIA DIAVEZUKA PELAGIE","departement":"Administration","grade":"D2","jobTitle":"Plant HR Manager","localisation":"Zamba"}</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="str">
+        <v>Carine.Ewuli</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <v>Carine Ewuli</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <v>CES</v>
+      </c>
+      <c r="D6" s="3" t="str">
+        <v>Carine.Ewuli@ppcdrc.cd</v>
+      </c>
+      <c r="E6" s="3" t="str">
+        <v>123</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <v>Actif</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <v>{"matricule":"70000265","nom":"EWULI SUKA Carine","departement":"Corporate Admin","grade":"D5","jobTitle":"Head of Human Resources","localisation":"Kinshasa"}</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.54296875"/>
     <col min="2" max="2" customWidth="1" width="13.6328125"/>
@@ -869,10 +869,36 @@
         <v>{"matricule":"70000265","nom":"EWULI SUKA Carine","departement":"Corporate Admin","grade":"D5","jobTitle":"Head of Human Resources","localisation":"Kinshasa"}</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="str">
+        <v>Gedeon.Massadi</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <v>Gedeon Massadi</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <v>GMS</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <v>Gedeon.Massadi@ppcdrc.cd</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <v>1083</v>
+      </c>
+      <c r="F7" s="3" t="str">
+        <v>Actif</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <v>{"matricule":"70000308","nom":"MASSADI GEDEON GEDEON","departement":"Human Resources","grade":"C1","jobTitle":"HR Administrator","localisation":"Kinshasa"}</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -811,7 +811,7 @@
         <v>Actif</v>
       </c>
       <c r="G4" s="3" t="str">
-        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.departements","label":"Départements","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
+        <v>[{"menuId":"employes.liste","label":"Liste employés","actions":{"view":true,"create":false,"edit":false,"delete":false,"export":true}},{"menuId":"employes.dependants","label":"Dependants","actions":{"view":true,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.check-documents","label":"Check documents","actions":{"view":true,"create":false,"edit":true,"delete":false,"export":false}},{"menuId":"employes.heures","label":"Heures sup. — Mon timesheet","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"employes.heures.dept","label":"Heures sup. — Département (planning &amp; OT de son département — Modifier = éditer le planning)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.all","label":"Heures sup. — Tous départements (planning &amp; OT)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.import","label":"Heures sup. — Import OT (menu contextuel carte semaine)","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"employes.heures.compilation","label":"Heures sup. — Compilation &amp; politique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.dashboard","label":"Dashboard","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.projects","label":"Projects","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"project.expenses","label":"Expenses details","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.historique","label":"Voyage — Historique","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.etablir","label":"Voyage — Établir","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"travel.attestation","label":"Attestation de service","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"factures.fournisseur.liste","label":"Liste","actions":{"view":true,"create":true,"edit":true,"delete":false,"export":true}},{"menuId":"factures.fournisseur.factures","label":"Factures","actions":{"view":true,"create":true,"edit":true,"delete":false,"export":true}},{"menuId":"factures.fournisseur.soa","label":"SOA","actions":{"view":true,"create":true,"edit":true,"delete":false,"export":true}},{"menuId":"factures.fournisseur.fournisseurs","label":"Fournisseurs","actions":{"view":true,"create":true,"edit":true,"delete":false,"export":true}},{"menuId":"sante","label":"Santé","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"charroi","label":"Charroi automobile","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"village.dependants-dashboard","label":"Dashboard (Village/Kimpese)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.dependants-liste","label":"Liste (Village/Kimpese)","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.maisons","label":"Maisons","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"village.guest-house","label":"Guest house — réservations &amp; occupation","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.departements","label":"Départements","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.centres","label":"Centre de coût","actions":{"view":true,"create":true,"edit":true,"delete":true,"export":true}},{"menuId":"settings.utilisateurs","label":"Utilisateurs","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}},{"menuId":"settings.permissions","label":"Permissions","actions":{"view":false,"create":false,"edit":false,"delete":false,"export":false}}]</v>
       </c>
       <c r="H4" s="3" t="str">
         <v>{"matricule":"70000008","nom":"MUAKASA NSONI SERGE","departement":"Human Resources","grade":"C4","jobTitle":"Estate Officer","localisation":"Zamba"}</v>

--- a/Excel/Params.xlsx
+++ b/Excel/Params.xlsx
@@ -135,10 +135,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -187,10 +187,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃ